--- a/Backend/Input/Adm_risk/Planilla_PTR.xlsx
+++ b/Backend/Input/Adm_risk/Planilla_PTR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29022"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca-my.sharepoint.com/personal/joaquin_astorga_mineduc_cl/Documents/Documentos/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ARMM/Gestión de Riesgos/Monitoreo PTR/2025/Julio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{8DA4E4B1-C671-4E79-8AC4-F799C28A0995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98D0DDEB-4778-420B-8156-47548CBF8E81}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{8DA4E4B1-C671-4E79-8AC4-F799C28A0995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2F32FF8-3788-4E8B-ACCC-9989DABD5027}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7D582672-387C-43DA-B99F-6DF608B8FC7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7D582672-387C-43DA-B99F-6DF608B8FC7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Herramienta_Monitoreo" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,8 +94,40 @@
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="14"/>
-      <color rgb="FFF2F2F2"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -105,25 +137,9 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFF2F2F2"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -185,15 +201,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color rgb="FF000000"/>
@@ -202,6 +209,19 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -216,7 +236,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -232,21 +254,17 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -266,17 +284,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -299,6 +306,15 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -339,63 +355,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -732,7 +751,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23DC285E-FD57-4D3B-B6AD-0131CE74D42F}">
   <dimension ref="B4:F19"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="2" width="39.140625" customWidth="1"/>
@@ -742,83 +761,88 @@
     <col min="6" max="6" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:5" ht="15" customHeight="1">
+    <row r="4" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="2:5" ht="15" customHeight="1">
+    <row r="5" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="17"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
     </row>
-    <row r="6" spans="2:5" ht="15" customHeight="1">
+    <row r="6" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="17"/>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="19" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="41.25" customHeight="1">
+    <row r="7" spans="2:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="18"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
     </row>
-    <row r="8" spans="2:5" ht="21">
+    <row r="8" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" s="5">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E8" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="21">
+    <row r="9" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D9" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="21">
+    <row r="10" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D10" s="5">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E10" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="33" customHeight="1">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+    </row>
+    <row r="17" spans="2:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
         <v>8</v>
       </c>
@@ -829,7 +853,7 @@
       <c r="E17" s="10"/>
       <c r="F17" s="11"/>
     </row>
-    <row r="18" spans="2:6" ht="34.5" customHeight="1">
+    <row r="18" spans="2:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
       <c r="C18" s="12" t="s">
         <v>10</v>
@@ -842,7 +866,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="27.75" customHeight="1">
+    <row r="19" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
         <v>13</v>
       </c>
@@ -851,10 +875,10 @@
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="6">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F19" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -864,22 +888,25 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="B4:B7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="C6:C7"/>
     <mergeCell ref="C4:E5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+    <orden xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1147,25 +1174,48 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-    <orden xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DD7C8A8-5791-4436-A622-886DDA5695C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18A04A5F-AA73-4640-9A45-FA0463B4A2FA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8ED488C-2573-49DB-8E1B-F5CFCC329B05}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8ED488C-2573-49DB-8E1B-F5CFCC329B05}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18A04A5F-AA73-4640-9A45-FA0463B4A2FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DD7C8A8-5791-4436-A622-886DDA5695C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>